--- a/data/trans_orig/Q4504_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>89949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127923</t>
+          <t>127054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>60831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91095</t>
+          <t>90715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158698</t>
+          <t>159293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208231</t>
+          <t>206560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116580</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155435</t>
+          <t>157170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102634</t>
+          <t>103288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197269</t>
+          <t>197892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246500</t>
+          <t>249245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100152</t>
+          <t>101410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140078</t>
+          <t>138069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>72229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>104644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>183499</t>
+          <t>184582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233205</t>
+          <t>234673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48538</t>
+          <t>49957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>35830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62157</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93748</t>
+          <t>93922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>31570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55845</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100407</t>
+          <t>101286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140876</t>
+          <t>141001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63439</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96476</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75608</t>
+          <t>77073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109605</t>
+          <t>110945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148036</t>
+          <t>148476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195950</t>
+          <t>197014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66624</t>
+          <t>66173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99907</t>
+          <t>99919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>67176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>100824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143265</t>
+          <t>142722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190789</t>
+          <t>188787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91299</t>
+          <t>90517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126305</t>
+          <t>124992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100173</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132857</t>
+          <t>132345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>198988</t>
+          <t>199452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248566</t>
+          <t>248401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89484</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>52789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81688</t>
+          <t>82753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118666</t>
+          <t>117619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160417</t>
+          <t>160815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>63870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97587</t>
+          <t>98093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24666</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45600</t>
+          <t>46366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95860</t>
+          <t>95769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135551</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98291</t>
+          <t>97868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>135717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126269</t>
+          <t>126032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170960</t>
+          <t>169141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140069</t>
+          <t>143154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184624</t>
+          <t>184151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59389</t>
+          <t>59549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>184796</t>
+          <t>184650</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237031</t>
+          <t>233802</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71858</t>
+          <t>70800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>88584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106900</t>
+          <t>107141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145585</t>
+          <t>145257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51382</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>145560</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189695</t>
+          <t>191172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154572</t>
+          <t>153859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204036</t>
+          <t>203584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121307</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161512</t>
+          <t>163378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>288198</t>
+          <t>284300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>353372</t>
+          <t>347918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195592</t>
+          <t>195824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250090</t>
+          <t>248701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134978</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>178216</t>
+          <t>180125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>343973</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>414108</t>
+          <t>410463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>313052</t>
+          <t>311035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>376205</t>
+          <t>372675</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>163805</t>
+          <t>162222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209402</t>
+          <t>210527</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>489467</t>
+          <t>488483</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>570274</t>
+          <t>573289</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81556</t>
+          <t>82622</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119685</t>
+          <t>118380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77989</t>
+          <t>80636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138464</t>
+          <t>135698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188280</t>
+          <t>184582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>360724</t>
+          <t>359845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>424205</t>
+          <t>425776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>194089</t>
+          <t>196828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526288</t>
+          <t>525732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>604124</t>
+          <t>605744</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44943</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>73863</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>86823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126870</t>
+          <t>125206</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142333</t>
+          <t>139270</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>188888</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53197</t>
+          <t>52789</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82615</t>
+          <t>84400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>80669</t>
+          <t>78931</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116470</t>
+          <t>116994</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>142430</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188457</t>
+          <t>186600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>89391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123129</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119073</t>
+          <t>119962</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160369</t>
+          <t>163558</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>215662</t>
+          <t>217448</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>270762</t>
+          <t>271762</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28194</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50464</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81786</t>
+          <t>81968</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>66083</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100762</t>
+          <t>102368</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>86336</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>122361</t>
+          <t>121068</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140367</t>
+          <t>140897</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>185524</t>
+          <t>184040</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>240849</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>294101</t>
+          <t>295302</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46359</t>
+          <t>46016</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>124645</t>
+          <t>129405</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>173750</t>
+          <t>176269</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>160280</t>
+          <t>158343</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>212356</t>
+          <t>210464</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>60380</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>90077</t>
+          <t>90114</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>155732</t>
+          <t>154841</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>204188</t>
+          <t>202424</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,42 +4305,42 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>253124</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>224087</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>281360</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>16,38%</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>253124</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>225175</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>281265</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>87638</t>
+          <t>87835</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>119619</t>
+          <t>119301</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>259421</t>
+          <t>256909</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>317059</t>
+          <t>317130</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>359939</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>424920</t>
+          <t>429599</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36541</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>91289</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131354</t>
+          <t>131786</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>115154</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>159278</t>
+          <t>160423</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>45705</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>75771</t>
+          <t>73402</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>484990</t>
+          <t>487490</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>554502</t>
+          <t>555512</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>543145</t>
+          <t>538522</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>617314</t>
+          <t>619899</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>497594</t>
+          <t>492815</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>582121</t>
+          <t>579447</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>549048</t>
+          <t>555242</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>641590</t>
+          <t>644046</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1077745</t>
+          <t>1079317</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1197448</t>
+          <t>1198739</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>648060</t>
+          <t>649705</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>743587</t>
+          <t>746234</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>585985</t>
+          <t>585057</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>679442</t>
+          <t>678543</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1268704</t>
+          <t>1264781</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1400270</t>
+          <t>1392597</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>883746</t>
+          <t>891683</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>993772</t>
+          <t>993410</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>817767</t>
+          <t>814914</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>920433</t>
+          <t>914156</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1727801</t>
+          <t>1731744</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1874341</t>
+          <t>1878204</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>230815</t>
+          <t>229161</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>296339</t>
+          <t>295420</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>246665</t>
+          <t>248070</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>310346</t>
+          <t>311562</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>496750</t>
+          <t>492011</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>584075</t>
+          <t>584680</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>784185</t>
+          <t>781808</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>881925</t>
+          <t>882922</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>952050</t>
+          <t>946954</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1058391</t>
+          <t>1050789</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1764261</t>
+          <t>1763143</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1913193</t>
+          <t>1904868</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121510</t>
+          <t>123633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164504</t>
+          <t>164793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>94535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132763</t>
+          <t>132344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229076</t>
+          <t>230584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283108</t>
+          <t>285066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113327</t>
+          <t>112239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155399</t>
+          <t>152851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74673</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107583</t>
+          <t>108458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197329</t>
+          <t>197891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250027</t>
+          <t>251095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65278</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99689</t>
+          <t>99916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>39269</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67814</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117131</t>
+          <t>114654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>159965</t>
+          <t>160728</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55467</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87316</t>
+          <t>90795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>98637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144322</t>
+          <t>141266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110336</t>
+          <t>112166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154149</t>
+          <t>154982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100305</t>
+          <t>101374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136389</t>
+          <t>137942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222200</t>
+          <t>226719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277895</t>
+          <t>279335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>94249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133227</t>
+          <t>133065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>81044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115109</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183236</t>
+          <t>185991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237563</t>
+          <t>238750</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92541</t>
+          <t>93549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106680</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152152</t>
+          <t>149389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34303</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>69192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103661</t>
+          <t>105324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71060</t>
+          <t>69692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118106</t>
+          <t>116522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165930</t>
+          <t>163578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>146003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191816</t>
+          <t>193176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>61623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93026</t>
+          <t>92451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217679</t>
+          <t>216662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>274094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110580</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151479</t>
+          <t>150640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47835</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74198</t>
+          <t>74830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164158</t>
+          <t>166139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214123</t>
+          <t>212649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101516</t>
+          <t>103188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142860</t>
+          <t>143293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>37406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146239</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195309</t>
+          <t>194176</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44261</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33366</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61535</t>
+          <t>59727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>152825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202161</t>
+          <t>198206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48281</t>
+          <t>48010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75879</t>
+          <t>75875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>211883</t>
+          <t>210664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266151</t>
+          <t>265171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>242205</t>
+          <t>239581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>300714</t>
+          <t>301583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198119</t>
+          <t>198530</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250909</t>
+          <t>252688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>460957</t>
+          <t>454176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>536761</t>
+          <t>536472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194561</t>
+          <t>192515</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248316</t>
+          <t>249766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169420</t>
+          <t>168748</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215611</t>
+          <t>218190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>377423</t>
+          <t>373869</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>446099</t>
+          <t>449234</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>185952</t>
+          <t>187111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>240942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112789</t>
+          <t>112252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155170</t>
+          <t>156886</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>312827</t>
+          <t>312218</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>381161</t>
+          <t>381878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61352</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52744</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86356</t>
+          <t>88242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>377418</t>
+          <t>375422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>442521</t>
+          <t>441478</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169772</t>
+          <t>169611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220852</t>
+          <t>221586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>560309</t>
+          <t>561542</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>643401</t>
+          <t>646422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>81876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118613</t>
+          <t>119058</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108534</t>
+          <t>107925</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151588</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>201991</t>
+          <t>199066</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>255410</t>
+          <t>254487</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108521</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128503</t>
+          <t>126458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173983</t>
+          <t>172236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>213379</t>
+          <t>215352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270266</t>
+          <t>270210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77326</t>
+          <t>77221</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114827</t>
+          <t>114722</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118331</t>
+          <t>120883</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>163164</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207824</t>
+          <t>209102</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>264220</t>
+          <t>264908</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>41672</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>47923</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49627</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81592</t>
+          <t>79806</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>172631</t>
+          <t>173089</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217871</t>
+          <t>217404</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>276715</t>
+          <t>276723</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>333025</t>
+          <t>332858</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>463813</t>
+          <t>466922</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>534714</t>
+          <t>536404</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>49346</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77389</t>
+          <t>76628</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>186224</t>
+          <t>188981</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>239873</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246932</t>
+          <t>246186</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>305170</t>
+          <t>307037</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>45774</t>
+          <t>46717</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>184618</t>
+          <t>184193</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>238014</t>
+          <t>235799</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>238211</t>
+          <t>239799</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>299024</t>
+          <t>299212</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>55728</t>
+          <t>56832</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>183707</t>
+          <t>180098</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>234454</t>
+          <t>234100</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>246298</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>307847</t>
+          <t>304010</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47060</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80862</t>
+          <t>78932</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>97736</t>
+          <t>98604</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46029</t>
+          <t>46466</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>73669</t>
+          <t>73381</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>381726</t>
+          <t>381983</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>447797</t>
+          <t>445047</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>438424</t>
+          <t>440530</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>513780</t>
+          <t>511363</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>821655</t>
+          <t>822979</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>929650</t>
+          <t>925890</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>823806</t>
+          <t>823193</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>925416</t>
+          <t>930052</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1683474</t>
+          <t>1680425</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1834759</t>
+          <t>1830373</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>693534</t>
+          <t>696246</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>799741</t>
+          <t>795080</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>749018</t>
+          <t>747689</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>851785</t>
+          <t>848150</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1467771</t>
+          <t>1481478</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1617937</t>
+          <t>1630003</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>608596</t>
+          <t>607106</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>705291</t>
+          <t>699663</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>584973</t>
+          <t>588622</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>680623</t>
+          <t>680122</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1226839</t>
+          <t>1214661</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1350112</t>
+          <t>1348993</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>119307</t>
+          <t>121706</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>165477</t>
+          <t>167180</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>127307</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>174554</t>
+          <t>172326</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>256433</t>
+          <t>259233</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>326602</t>
+          <t>327112</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>939314</t>
+          <t>943053</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1054903</t>
+          <t>1053163</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1017368</t>
+          <t>1023831</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1138664</t>
+          <t>1132495</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1994237</t>
+          <t>1993813</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2150216</t>
+          <t>2154367</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112674</t>
+          <t>113291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153946</t>
+          <t>154682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120348</t>
+          <t>120207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158495</t>
+          <t>157953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244559</t>
+          <t>245681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299770</t>
+          <t>299307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121086</t>
+          <t>118425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>97002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131565</t>
+          <t>132495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229887</t>
+          <t>228629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281433</t>
+          <t>281373</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57139</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90442</t>
+          <t>86913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>94394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>135463</t>
+          <t>133633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54968</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87361</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87361</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126380</t>
+          <t>126424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92856</t>
+          <t>94783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130266</t>
+          <t>132514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107223</t>
+          <t>106831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143364</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210742</t>
+          <t>211085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264504</t>
+          <t>262270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107141</t>
+          <t>107717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144691</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114395</t>
+          <t>113879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151767</t>
+          <t>150731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231514</t>
+          <t>232439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282094</t>
+          <t>283120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69890</t>
+          <t>70290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39712</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89148</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127454</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55840</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>86237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58839</t>
+          <t>57893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137421</t>
+          <t>135147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94087</t>
+          <t>94224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>132789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55285</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130749</t>
+          <t>133544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176451</t>
+          <t>178535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140264</t>
+          <t>138243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183630</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48976</t>
+          <t>49047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74571</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196194</t>
+          <t>198160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249068</t>
+          <t>246703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>66570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99798</t>
+          <t>98980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84238</t>
+          <t>83435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>120943</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115304</t>
+          <t>116885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156780</t>
+          <t>158735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25797</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>148213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199327</t>
+          <t>196284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>194137</t>
+          <t>192898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>247972</t>
+          <t>244300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193536</t>
+          <t>195657</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>245364</t>
+          <t>246158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>399388</t>
+          <t>399120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>472317</t>
+          <t>475121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>338175</t>
+          <t>336857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>399276</t>
+          <t>401400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244041</t>
+          <t>247116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299710</t>
+          <t>297368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>596347</t>
+          <t>596722</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>679920</t>
+          <t>678378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>181078</t>
+          <t>181128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>233277</t>
+          <t>235216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123863</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166079</t>
+          <t>167564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>319447</t>
+          <t>313569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>386351</t>
+          <t>382426</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41546</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>68786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72024</t>
+          <t>73093</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106972</t>
+          <t>108293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268850</t>
+          <t>268585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328962</t>
+          <t>328578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131108</t>
+          <t>132461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174870</t>
+          <t>174896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>415014</t>
+          <t>414432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>487768</t>
+          <t>491844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67898</t>
+          <t>67477</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104117</t>
+          <t>103533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129783</t>
+          <t>128895</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>175657</t>
+          <t>173969</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211129</t>
+          <t>212259</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>266908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143047</t>
+          <t>143793</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>189496</t>
+          <t>188144</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>174284</t>
+          <t>174778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222153</t>
+          <t>223321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>328985</t>
+          <t>329881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>396162</t>
+          <t>394278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73409</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110234</t>
+          <t>109716</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128451</t>
+          <t>129607</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>173855</t>
+          <t>174598</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228876</t>
+          <t>231243</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32542</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>57782</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64931</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103594</t>
+          <t>101812</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>210048</t>
+          <t>212129</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>259086</t>
+          <t>260647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>213379</t>
+          <t>214243</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>266249</t>
+          <t>267510</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>437606</t>
+          <t>438584</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>511911</t>
+          <t>509284</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77781</t>
+          <t>76892</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>172694</t>
+          <t>171874</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>224007</t>
+          <t>225132</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>231064</t>
+          <t>231591</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>289042</t>
+          <t>292142</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>85498</t>
+          <t>85607</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>118453</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>304339</t>
+          <t>302527</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>371165</t>
+          <t>368614</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>401631</t>
+          <t>401480</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>470041</t>
+          <t>470893</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>39016</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>137079</t>
+          <t>138163</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>186854</t>
+          <t>185268</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>188403</t>
+          <t>185450</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>243584</t>
+          <t>242447</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45561</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>78096</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>56713</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>93274</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>44814</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72227</t>
+          <t>73371</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>291780</t>
+          <t>293521</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>358670</t>
+          <t>356091</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>350237</t>
+          <t>348154</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>422068</t>
+          <t>417703</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>674669</t>
+          <t>676352</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>773856</t>
+          <t>773954</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>823740</t>
+          <t>823043</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>924491</t>
+          <t>924994</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1528587</t>
+          <t>1524854</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1667486</t>
+          <t>1667082</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1008733</t>
+          <t>1007965</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1114114</t>
+          <t>1123589</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1057498</t>
+          <t>1058412</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1172809</t>
+          <t>1172127</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2083022</t>
+          <t>2096261</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2251816</t>
+          <t>2244919</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>514526</t>
+          <t>510999</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>600288</t>
+          <t>598376</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>483387</t>
+          <t>489537</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>574456</t>
+          <t>575223</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1020802</t>
+          <t>1024123</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1143208</t>
+          <t>1140856</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>146286</t>
+          <t>143672</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>194779</t>
+          <t>193690</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>147538</t>
+          <t>147870</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>197571</t>
+          <t>197470</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>305652</t>
+          <t>304274</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>375876</t>
+          <t>378314</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>813631</t>
+          <t>813189</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>917452</t>
+          <t>913655</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>784989</t>
+          <t>781225</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>891762</t>
+          <t>887691</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1624697</t>
+          <t>1632157</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1777004</t>
+          <t>1780187</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4504_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89949</t>
+          <t>89041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127054</t>
+          <t>126836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>61896</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>91952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159293</t>
+          <t>156656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206560</t>
+          <t>205700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>114433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157170</t>
+          <t>155156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>70227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103288</t>
+          <t>102580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197892</t>
+          <t>197235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249245</t>
+          <t>248380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101410</t>
+          <t>99527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138069</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,47 +973,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>89002</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>73512</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>105433</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89002</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>72229</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104644</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>29,14%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184582</t>
+          <t>182389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234673</t>
+          <t>235338</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49957</t>
+          <t>48493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>62533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93922</t>
+          <t>94587</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101286</t>
+          <t>100404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141001</t>
+          <t>142464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>64502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>97689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77073</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110945</t>
+          <t>109151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148476</t>
+          <t>148790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197014</t>
+          <t>197985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66173</t>
+          <t>66006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>100212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67176</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100824</t>
+          <t>100539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142722</t>
+          <t>143947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188787</t>
+          <t>187775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90517</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124992</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96791</t>
+          <t>99109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132345</t>
+          <t>134028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199452</t>
+          <t>199707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248401</t>
+          <t>247778</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>36923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53206</t>
+          <t>53182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59753</t>
+          <t>59505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89564</t>
+          <t>88927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82753</t>
+          <t>80409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117619</t>
+          <t>118351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160815</t>
+          <t>160199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63870</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98093</t>
+          <t>99523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95769</t>
+          <t>96066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>135788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97868</t>
+          <t>98235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135717</t>
+          <t>134698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41846</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126032</t>
+          <t>126797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169141</t>
+          <t>169808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184151</t>
+          <t>185550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59549</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>184650</t>
+          <t>185303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>233802</t>
+          <t>233669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>44045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>56228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88584</t>
+          <t>87637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107141</t>
+          <t>106519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145257</t>
+          <t>146049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>52527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144311</t>
+          <t>145388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191172</t>
+          <t>190345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153859</t>
+          <t>154983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203584</t>
+          <t>206482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,47 +2793,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>139483</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>117709</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>160634</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>16,48%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>139483</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>118972</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>163378</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284300</t>
+          <t>284555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347918</t>
+          <t>351445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>197364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248701</t>
+          <t>248900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134137</t>
+          <t>134042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180125</t>
+          <t>177248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>410463</t>
+          <t>416865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>311035</t>
+          <t>313246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>372675</t>
+          <t>376871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162222</t>
+          <t>164853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210527</t>
+          <t>212695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>488483</t>
+          <t>489963</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>573289</t>
+          <t>573432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82622</t>
+          <t>82806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118380</t>
+          <t>120657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,82 +3132,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>63021</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>48989</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>80689</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>162222</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>141607</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>186723</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>63021</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>48843</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>80636</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>162222</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>135698</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>184582</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>359845</t>
+          <t>360627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>425776</t>
+          <t>424629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150258</t>
+          <t>150146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>196828</t>
+          <t>196527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>525732</t>
+          <t>517197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>605744</t>
+          <t>599478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>45029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73863</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86823</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>125206</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>139270</t>
+          <t>140632</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>188910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84400</t>
+          <t>83154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78931</t>
+          <t>79091</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116994</t>
+          <t>114840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>141251</t>
+          <t>139792</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>186600</t>
+          <t>186887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89391</t>
+          <t>86174</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122420</t>
+          <t>121419</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119962</t>
+          <t>118479</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163558</t>
+          <t>161650</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>217448</t>
+          <t>217735</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271762</t>
+          <t>271699</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81968</t>
+          <t>80963</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>102368</t>
+          <t>100436</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>86336</t>
+          <t>86901</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>121068</t>
+          <t>121295</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140897</t>
+          <t>142830</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>184040</t>
+          <t>185702</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>240849</t>
+          <t>240171</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>295302</t>
+          <t>295791</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46016</t>
+          <t>44666</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>129405</t>
+          <t>127536</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>176269</t>
+          <t>175685</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>158343</t>
+          <t>160969</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>210464</t>
+          <t>213567</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>61282</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>90114</t>
+          <t>89659</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>154841</t>
+          <t>155756</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>202424</t>
+          <t>203397</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>224087</t>
+          <t>224707</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>281360</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>87835</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>121952</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>256909</t>
+          <t>259869</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>317130</t>
+          <t>318829</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>359939</t>
+          <t>362751</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>429599</t>
+          <t>427858</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>91289</t>
+          <t>91482</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131786</t>
+          <t>130545</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>114532</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>160423</t>
+          <t>159116</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>73402</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>487490</t>
+          <t>486706</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>555512</t>
+          <t>555268</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>538522</t>
+          <t>542194</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>619899</t>
+          <t>615343</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>492815</t>
+          <t>497524</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>579447</t>
+          <t>583577</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>555242</t>
+          <t>554081</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>644046</t>
+          <t>643375</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1079317</t>
+          <t>1073836</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1198739</t>
+          <t>1198707</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>649705</t>
+          <t>649725</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>746234</t>
+          <t>744177</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>585057</t>
+          <t>585777</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>678543</t>
+          <t>673778</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1264781</t>
+          <t>1262410</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1392597</t>
+          <t>1391141</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>891683</t>
+          <t>890818</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>993410</t>
+          <t>993181</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>814914</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>914156</t>
+          <t>913559</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1731744</t>
+          <t>1731336</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1878204</t>
+          <t>1872681</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>229161</t>
+          <t>229796</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>295420</t>
+          <t>291113</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>248070</t>
+          <t>247099</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>311562</t>
+          <t>308028</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>492011</t>
+          <t>496852</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>584680</t>
+          <t>586298</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>781808</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>882922</t>
+          <t>884213</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>946954</t>
+          <t>949975</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1050789</t>
+          <t>1058885</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1763143</t>
+          <t>1763025</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1904868</t>
+          <t>1911102</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123633</t>
+          <t>122665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164793</t>
+          <t>165373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>96682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>132758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230584</t>
+          <t>232052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285066</t>
+          <t>285933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112239</t>
+          <t>113768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152851</t>
+          <t>155191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>75927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108458</t>
+          <t>108465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197891</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251095</t>
+          <t>253941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99916</t>
+          <t>101841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68202</t>
+          <t>69209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114654</t>
+          <t>113377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160728</t>
+          <t>158112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56108</t>
+          <t>56227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90795</t>
+          <t>88889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62283</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98637</t>
+          <t>99612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141266</t>
+          <t>143181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112166</t>
+          <t>111139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154982</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101374</t>
+          <t>101015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>136623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226719</t>
+          <t>225687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279335</t>
+          <t>278839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94249</t>
+          <t>95816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133065</t>
+          <t>134140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81044</t>
+          <t>79342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115773</t>
+          <t>115255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185991</t>
+          <t>185550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238750</t>
+          <t>236957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>92670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>39633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69674</t>
+          <t>69671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105698</t>
+          <t>107884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149389</t>
+          <t>149847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69192</t>
+          <t>69196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105324</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>42624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116522</t>
+          <t>118017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163578</t>
+          <t>164153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146003</t>
+          <t>146174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193176</t>
+          <t>191840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61623</t>
+          <t>62897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92451</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216662</t>
+          <t>219261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274094</t>
+          <t>275984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109025</t>
+          <t>111341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150640</t>
+          <t>151881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>46629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74830</t>
+          <t>74197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166139</t>
+          <t>164505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212649</t>
+          <t>215679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103188</t>
+          <t>102356</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143293</t>
+          <t>141033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63213</t>
+          <t>60866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145262</t>
+          <t>147105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194176</t>
+          <t>194083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>60300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>152207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198206</t>
+          <t>200874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48010</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75875</t>
+          <t>75787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210664</t>
+          <t>210932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265171</t>
+          <t>261523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239581</t>
+          <t>238850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>301583</t>
+          <t>300525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198530</t>
+          <t>199930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252688</t>
+          <t>250130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>454176</t>
+          <t>452129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>536472</t>
+          <t>536243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192515</t>
+          <t>190277</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249766</t>
+          <t>245217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168748</t>
+          <t>168375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>218190</t>
+          <t>215503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>373869</t>
+          <t>374984</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>449234</t>
+          <t>450625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187111</t>
+          <t>187036</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240942</t>
+          <t>240682</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112252</t>
+          <t>112794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156886</t>
+          <t>155595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>312218</t>
+          <t>313985</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>381878</t>
+          <t>385665</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>34504</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60839</t>
+          <t>59805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>85540</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>375422</t>
+          <t>375801</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>441478</t>
+          <t>444025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169611</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221586</t>
+          <t>218895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>561542</t>
+          <t>556299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>646422</t>
+          <t>640524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>81876</t>
+          <t>83128</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>119058</t>
+          <t>120848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107925</t>
+          <t>106705</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150966</t>
+          <t>150661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>199084</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>254487</t>
+          <t>253769</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75047</t>
+          <t>74978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109856</t>
+          <t>110339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126458</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>172236</t>
+          <t>173662</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215352</t>
+          <t>214448</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270210</t>
+          <t>272975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77221</t>
+          <t>75993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114067</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120883</t>
+          <t>121106</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163164</t>
+          <t>163959</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>209102</t>
+          <t>207010</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>264908</t>
+          <t>262147</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>42704</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>49231</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>79806</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>173089</t>
+          <t>172496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217404</t>
+          <t>217181</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>276723</t>
+          <t>277984</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>332858</t>
+          <t>331445</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>466922</t>
+          <t>467190</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>536404</t>
+          <t>535401</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>76628</t>
+          <t>79281</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>188981</t>
+          <t>186360</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>240730</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246186</t>
+          <t>249062</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>307037</t>
+          <t>307105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>46717</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>72990</t>
+          <t>73437</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>184193</t>
+          <t>183833</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>235799</t>
+          <t>237757</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>239799</t>
+          <t>242395</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>299212</t>
+          <t>299910</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>84531</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>180098</t>
+          <t>185500</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>234100</t>
+          <t>232504</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>246298</t>
+          <t>248325</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>304010</t>
+          <t>305443</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47060</t>
+          <t>49999</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78932</t>
+          <t>79336</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>60541</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>98604</t>
+          <t>95513</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46466</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>73381</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>381983</t>
+          <t>383583</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>445047</t>
+          <t>448254</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>440530</t>
+          <t>438670</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>511363</t>
+          <t>510495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>822979</t>
+          <t>822311</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>925890</t>
+          <t>936245</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>823193</t>
+          <t>823637</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>930052</t>
+          <t>930425</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1680425</t>
+          <t>1672620</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1830373</t>
+          <t>1819743</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>696246</t>
+          <t>697695</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>795080</t>
+          <t>797011</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>747689</t>
+          <t>746684</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>848150</t>
+          <t>852921</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1481478</t>
+          <t>1460409</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1630003</t>
+          <t>1609321</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>607106</t>
+          <t>602164</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>699663</t>
+          <t>701448</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>588622</t>
+          <t>589477</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>680122</t>
+          <t>682603</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1214661</t>
+          <t>1223688</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1348993</t>
+          <t>1357552</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>120275</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>167180</t>
+          <t>167715</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>127307</t>
+          <t>125081</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>172326</t>
+          <t>175468</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>259233</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>327112</t>
+          <t>323996</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>943053</t>
+          <t>940919</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1053163</t>
+          <t>1051585</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1023831</t>
+          <t>1020075</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1132495</t>
+          <t>1132483</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1993813</t>
+          <t>1996664</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2154367</t>
+          <t>2155737</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113291</t>
+          <t>112592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154682</t>
+          <t>151878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120207</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157953</t>
+          <t>158056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245681</t>
+          <t>243719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299307</t>
+          <t>298910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118425</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159139</t>
+          <t>160913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97002</t>
+          <t>97007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132495</t>
+          <t>131038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>230450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281373</t>
+          <t>283866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>87224</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>55597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94394</t>
+          <t>94638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133633</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>39990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85794</t>
+          <t>86850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89228</t>
+          <t>88836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126424</t>
+          <t>129387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94783</t>
+          <t>92740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>129298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106831</t>
+          <t>105639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143418</t>
+          <t>144602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>211085</t>
+          <t>209456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262270</t>
+          <t>262493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>106763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146346</t>
+          <t>144418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113879</t>
+          <t>112119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150731</t>
+          <t>150837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232439</t>
+          <t>233994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283120</t>
+          <t>285008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70290</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66795</t>
+          <t>67433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88890</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127268</t>
+          <t>128733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54586</t>
+          <t>54926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86237</t>
+          <t>85075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33341</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57893</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93036</t>
+          <t>96201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135147</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94224</t>
+          <t>94270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132789</t>
+          <t>133996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54738</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133544</t>
+          <t>133692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178535</t>
+          <t>178349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138243</t>
+          <t>140636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180706</t>
+          <t>183434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49047</t>
+          <t>49130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198160</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246703</t>
+          <t>248629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>63805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98980</t>
+          <t>98537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83435</t>
+          <t>83971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120943</t>
+          <t>123565</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>20025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116885</t>
+          <t>116069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158735</t>
+          <t>158099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27034</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50044</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148213</t>
+          <t>151008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196284</t>
+          <t>198554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192898</t>
+          <t>194912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>244300</t>
+          <t>248365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195657</t>
+          <t>192121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246158</t>
+          <t>245394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>399120</t>
+          <t>400303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475121</t>
+          <t>474730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>336857</t>
+          <t>336559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>401400</t>
+          <t>399922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247116</t>
+          <t>244897</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297368</t>
+          <t>302625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>596722</t>
+          <t>598312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678378</t>
+          <t>680180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>181128</t>
+          <t>181344</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235216</t>
+          <t>232322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123303</t>
+          <t>123433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167564</t>
+          <t>167740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313569</t>
+          <t>316440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>382426</t>
+          <t>383977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39587</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73093</t>
+          <t>70891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108293</t>
+          <t>107693</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268585</t>
+          <t>268775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328578</t>
+          <t>327718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132461</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174896</t>
+          <t>178395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>414432</t>
+          <t>415932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>491844</t>
+          <t>487202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>67646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103533</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>128895</t>
+          <t>130719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>173969</t>
+          <t>175617</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212259</t>
+          <t>209085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266908</t>
+          <t>265654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143793</t>
+          <t>144508</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>188678</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>174778</t>
+          <t>172212</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>223321</t>
+          <t>221774</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>329881</t>
+          <t>331008</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>394278</t>
+          <t>397197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74345</t>
+          <t>73540</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109716</t>
+          <t>110891</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>91555</t>
+          <t>89495</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>129607</t>
+          <t>128251</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>174598</t>
+          <t>174517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>231243</t>
+          <t>227272</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>66033</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>101812</t>
+          <t>102588</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>212129</t>
+          <t>210486</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>260647</t>
+          <t>260932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>214243</t>
+          <t>213063</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>267510</t>
+          <t>265741</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>438584</t>
+          <t>439080</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>509284</t>
+          <t>508005</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>49369</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>76892</t>
+          <t>77268</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>171874</t>
+          <t>171469</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>225132</t>
+          <t>224503</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>231591</t>
+          <t>232729</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>292142</t>
+          <t>290081</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>85607</t>
+          <t>83969</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>117833</t>
+          <t>118435</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>302527</t>
+          <t>304010</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>368614</t>
+          <t>365591</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>401480</t>
+          <t>399683</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>470893</t>
+          <t>469884</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>65053</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138163</t>
+          <t>138385</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>185268</t>
+          <t>185670</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>185450</t>
+          <t>187032</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>242447</t>
+          <t>241409</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>56713</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>91360</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>44991</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>73246</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>293521</t>
+          <t>294338</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>356091</t>
+          <t>357361</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>348154</t>
+          <t>347264</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>417703</t>
+          <t>415619</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>676352</t>
+          <t>673981</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>773954</t>
+          <t>772262</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>823043</t>
+          <t>825107</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>924994</t>
+          <t>931621</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1524854</t>
+          <t>1529627</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1667082</t>
+          <t>1670899</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1007965</t>
+          <t>1007975</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1123589</t>
+          <t>1116803</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1058412</t>
+          <t>1055845</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1172127</t>
+          <t>1167937</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2096261</t>
+          <t>2095158</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2244919</t>
+          <t>2249258</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>510999</t>
+          <t>517192</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>598376</t>
+          <t>602606</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>489537</t>
+          <t>486156</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>575223</t>
+          <t>568596</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1024123</t>
+          <t>1021434</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1140856</t>
+          <t>1144715</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>143672</t>
+          <t>145477</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>193690</t>
+          <t>196167</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>147870</t>
+          <t>147989</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>197470</t>
+          <t>199548</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>304274</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>378314</t>
+          <t>378373</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>813189</t>
+          <t>812169</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>913655</t>
+          <t>917859</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>781225</t>
+          <t>787060</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>887691</t>
+          <t>888299</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1632157</t>
+          <t>1629124</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1780187</t>
+          <t>1777406</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
